--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_s_2020_antofagasta.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_s_2020_antofagasta.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:41</t>
+    <t xml:space="preserve">2026-10-05 02:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>417550.12</v>
+        <v>417550.13</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>307439.06</v>
@@ -505,7 +505,7 @@
         <v>450806.88</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>325846.62</v>
+        <v>325846.63</v>
       </c>
     </row>
     <row r="4">
@@ -601,7 +601,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>620489.12</v>
+        <v>620489.13</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433235.75</v>
@@ -612,7 +612,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>647482.12</v>
+        <v>647482.13</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>446666.81</v>
